--- a/RACKS_C12.xlsx
+++ b/RACKS_C12.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="347">
   <si>
     <t>Origen</t>
   </si>
@@ -52,7 +52,7 @@
     <t>A.2</t>
   </si>
   <si>
-    <t>PLAYER A</t>
+    <t>Player A</t>
   </si>
   <si>
     <t>Out 1</t>
@@ -82,7 +82,7 @@
     <t>A.3</t>
   </si>
   <si>
-    <t>PLAYER B</t>
+    <t>Player B</t>
   </si>
   <si>
     <t>In 2</t>
@@ -94,7 +94,7 @@
     <t>A.4</t>
   </si>
   <si>
-    <t>PLAYER C</t>
+    <t>Player C</t>
   </si>
   <si>
     <t>In 3</t>
@@ -127,7 +127,7 @@
     <t>B.2</t>
   </si>
   <si>
-    <t>LOOP A</t>
+    <t>Loop A</t>
   </si>
   <si>
     <t>Out 17</t>
@@ -139,7 +139,7 @@
     <t>B.3</t>
   </si>
   <si>
-    <t>LOOP B</t>
+    <t>Loop B</t>
   </si>
   <si>
     <t>Out 19</t>
@@ -151,7 +151,7 @@
     <t>B.4</t>
   </si>
   <si>
-    <t>LOOP C</t>
+    <t>Loop C</t>
   </si>
   <si>
     <t>Out 21</t>
@@ -172,9 +172,6 @@
     <t>PLAYER A.1</t>
   </si>
   <si>
-    <t>Player A</t>
-  </si>
-  <si>
     <t>MATRIZ 1</t>
   </si>
   <si>
@@ -187,18 +184,12 @@
     <t>PLAYER B.1</t>
   </si>
   <si>
-    <t>Player B</t>
-  </si>
-  <si>
     <t>MATRIZ 2</t>
   </si>
   <si>
     <t>PLAYER C.1</t>
   </si>
   <si>
-    <t>Player C</t>
-  </si>
-  <si>
     <t>MATRIZ 3</t>
   </si>
   <si>
@@ -292,7 +283,7 @@
     <t>C.4</t>
   </si>
   <si>
-    <t>Blackmagic MultiView</t>
+    <t>Blackmagic Multiview 16</t>
   </si>
   <si>
     <t>In 11</t>
@@ -373,9 +364,6 @@
     <t>LOOP A.1</t>
   </si>
   <si>
-    <t>Loop A</t>
-  </si>
-  <si>
     <t>IRD TV P.</t>
   </si>
   <si>
@@ -397,9 +385,6 @@
     <t>LOOP B.1</t>
   </si>
   <si>
-    <t>Loop B</t>
-  </si>
-  <si>
     <t>IRD CIS.H/V</t>
   </si>
   <si>
@@ -427,9 +412,6 @@
     <t>LOOP C.1</t>
   </si>
   <si>
-    <t>Loop C</t>
-  </si>
-  <si>
     <t>GRAB GV</t>
   </si>
   <si>
@@ -457,9 +439,6 @@
     <t>1 MV TX</t>
   </si>
   <si>
-    <t>Blackmagic MultiView 16</t>
-  </si>
-  <si>
     <t>CISCO 2</t>
   </si>
   <si>
@@ -532,6 +511,9 @@
     <t>F.6</t>
   </si>
   <si>
+    <t>Blackmagic Multiview 4</t>
+  </si>
+  <si>
     <t>D.L.1 Streaming</t>
   </si>
   <si>
@@ -703,9 +685,6 @@
     <t>D.11</t>
   </si>
   <si>
-    <t>Aja fs4</t>
-  </si>
-  <si>
     <t>AJA FS4</t>
   </si>
   <si>
@@ -814,9 +793,6 @@
     <t>MV TX</t>
   </si>
   <si>
-    <t>Blackmagic Multiview 16</t>
-  </si>
-  <si>
     <t>in 64</t>
   </si>
   <si>
@@ -953,9 +929,6 @@
   </si>
   <si>
     <t>Analog Audio L</t>
-  </si>
-  <si>
-    <t>D.CAM</t>
   </si>
   <si>
     <t>Yamaha QL5</t>
@@ -1311,7 +1284,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1326,10 +1299,10 @@
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1963,7 +1936,7 @@
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>4</v>
@@ -1993,7 +1966,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="44"/>
@@ -2007,10 +1980,10 @@
       <c r="A4" s="39"/>
       <c r="B4" s="45"/>
       <c r="C4" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E4" s="46"/>
       <c r="F4" s="46"/>
@@ -2022,10 +1995,10 @@
       <c r="A5" s="37"/>
       <c r="B5" s="43"/>
       <c r="C5" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E5" s="44"/>
       <c r="F5" s="44"/>
@@ -2037,10 +2010,10 @@
       <c r="A6" s="39"/>
       <c r="B6" s="45"/>
       <c r="C6" s="45" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E6" s="46"/>
       <c r="F6" s="46"/>
@@ -2052,10 +2025,10 @@
       <c r="A7" s="37"/>
       <c r="B7" s="43"/>
       <c r="C7" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
@@ -2067,10 +2040,10 @@
       <c r="A8" s="39"/>
       <c r="B8" s="45"/>
       <c r="C8" s="45" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E8" s="46"/>
       <c r="F8" s="46"/>
@@ -2082,10 +2055,10 @@
       <c r="A9" s="37"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
@@ -2097,10 +2070,10 @@
       <c r="A10" s="39"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E10" s="46"/>
       <c r="F10" s="46"/>
@@ -2112,10 +2085,10 @@
       <c r="A11" s="37"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E11" s="44"/>
       <c r="F11" s="44"/>
@@ -2127,10 +2100,10 @@
       <c r="A12" s="39"/>
       <c r="B12" s="45"/>
       <c r="C12" s="45" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E12" s="46"/>
       <c r="F12" s="46"/>
@@ -2142,10 +2115,10 @@
       <c r="A13" s="37"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E13" s="44"/>
       <c r="F13" s="44"/>
@@ -2169,7 +2142,7 @@
         <v>2.0</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="44"/>
@@ -2182,10 +2155,10 @@
       <c r="A16" s="39"/>
       <c r="B16" s="45"/>
       <c r="C16" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E16" s="46"/>
       <c r="F16" s="46"/>
@@ -2196,10 +2169,10 @@
       <c r="A17" s="37"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E17" s="44"/>
       <c r="F17" s="44"/>
@@ -2210,10 +2183,10 @@
       <c r="A18" s="39"/>
       <c r="B18" s="45"/>
       <c r="C18" s="45" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D18" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E18" s="46"/>
       <c r="F18" s="46"/>
@@ -2224,10 +2197,10 @@
       <c r="A19" s="37"/>
       <c r="B19" s="43"/>
       <c r="C19" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D19" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
@@ -2238,10 +2211,10 @@
       <c r="A20" s="39"/>
       <c r="B20" s="45"/>
       <c r="C20" s="45" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E20" s="46"/>
       <c r="F20" s="46"/>
@@ -2252,10 +2225,10 @@
       <c r="A21" s="37"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E21" s="44"/>
       <c r="F21" s="44"/>
@@ -2266,10 +2239,10 @@
       <c r="A22" s="39"/>
       <c r="B22" s="45"/>
       <c r="C22" s="45" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E22" s="46"/>
       <c r="F22" s="46"/>
@@ -2280,10 +2253,10 @@
       <c r="A23" s="37"/>
       <c r="B23" s="43"/>
       <c r="C23" s="43" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E23" s="44"/>
       <c r="F23" s="44"/>
@@ -2294,10 +2267,10 @@
       <c r="A24" s="39"/>
       <c r="B24" s="45"/>
       <c r="C24" s="45" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E24" s="46"/>
       <c r="F24" s="46"/>
@@ -2308,10 +2281,10 @@
       <c r="A25" s="37"/>
       <c r="B25" s="43"/>
       <c r="C25" s="43" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E25" s="44"/>
       <c r="F25" s="44"/>
@@ -2333,7 +2306,7 @@
         <v>3.0</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C27" s="43"/>
       <c r="D27" s="44"/>
@@ -2346,10 +2319,10 @@
       <c r="A28" s="39"/>
       <c r="B28" s="45"/>
       <c r="C28" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E28" s="46"/>
       <c r="F28" s="46"/>
@@ -2360,10 +2333,10 @@
       <c r="A29" s="37"/>
       <c r="B29" s="43"/>
       <c r="C29" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E29" s="44"/>
       <c r="F29" s="44"/>
@@ -2374,10 +2347,10 @@
       <c r="A30" s="39"/>
       <c r="B30" s="45"/>
       <c r="C30" s="45" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D30" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E30" s="46"/>
       <c r="F30" s="46"/>
@@ -2388,10 +2361,10 @@
       <c r="A31" s="37"/>
       <c r="B31" s="43"/>
       <c r="C31" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
@@ -2402,10 +2375,10 @@
       <c r="A32" s="39"/>
       <c r="B32" s="45"/>
       <c r="C32" s="45" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E32" s="46"/>
       <c r="F32" s="46"/>
@@ -2416,10 +2389,10 @@
       <c r="A33" s="37"/>
       <c r="B33" s="43"/>
       <c r="C33" s="43" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E33" s="44"/>
       <c r="F33" s="44"/>
@@ -2430,10 +2403,10 @@
       <c r="A34" s="39"/>
       <c r="B34" s="45"/>
       <c r="C34" s="45" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E34" s="46"/>
       <c r="F34" s="46"/>
@@ -2444,10 +2417,10 @@
       <c r="A35" s="37"/>
       <c r="B35" s="43"/>
       <c r="C35" s="43" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E35" s="44"/>
       <c r="F35" s="44"/>
@@ -2458,10 +2431,10 @@
       <c r="A36" s="39"/>
       <c r="B36" s="45"/>
       <c r="C36" s="45" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E36" s="46"/>
       <c r="F36" s="46"/>
@@ -2472,10 +2445,10 @@
       <c r="A37" s="37"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E37" s="44"/>
       <c r="F37" s="44"/>
@@ -2497,7 +2470,7 @@
         <v>4.0</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C39" s="43"/>
       <c r="D39" s="44"/>
@@ -2510,10 +2483,10 @@
       <c r="A40" s="39"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E40" s="46"/>
       <c r="F40" s="46"/>
@@ -2524,10 +2497,10 @@
       <c r="A41" s="37"/>
       <c r="B41" s="43"/>
       <c r="C41" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E41" s="44"/>
       <c r="F41" s="44"/>
@@ -2538,10 +2511,10 @@
       <c r="A42" s="39"/>
       <c r="B42" s="45"/>
       <c r="C42" s="45" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D42" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E42" s="46"/>
       <c r="F42" s="46"/>
@@ -2552,10 +2525,10 @@
       <c r="A43" s="37"/>
       <c r="B43" s="43"/>
       <c r="C43" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E43" s="44"/>
       <c r="F43" s="44"/>
@@ -2566,10 +2539,10 @@
       <c r="A44" s="39"/>
       <c r="B44" s="45"/>
       <c r="C44" s="45" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E44" s="46"/>
       <c r="F44" s="46"/>
@@ -2580,10 +2553,10 @@
       <c r="A45" s="37"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -2594,10 +2567,10 @@
       <c r="A46" s="39"/>
       <c r="B46" s="45"/>
       <c r="C46" s="45" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E46" s="46"/>
       <c r="F46" s="46"/>
@@ -2608,10 +2581,10 @@
       <c r="A47" s="37"/>
       <c r="B47" s="43"/>
       <c r="C47" s="43" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -2622,10 +2595,10 @@
       <c r="A48" s="39"/>
       <c r="B48" s="45"/>
       <c r="C48" s="45" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E48" s="46"/>
       <c r="F48" s="46"/>
@@ -2636,10 +2609,10 @@
       <c r="A49" s="37"/>
       <c r="B49" s="43"/>
       <c r="C49" s="43" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E49" s="44"/>
       <c r="F49" s="44"/>
@@ -2661,7 +2634,7 @@
         <v>5.0</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C51" s="43"/>
       <c r="D51" s="44"/>
@@ -2674,10 +2647,10 @@
       <c r="A52" s="39"/>
       <c r="B52" s="45"/>
       <c r="C52" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D52" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E52" s="46"/>
       <c r="F52" s="46"/>
@@ -2688,10 +2661,10 @@
       <c r="A53" s="37"/>
       <c r="B53" s="43"/>
       <c r="C53" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D53" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E53" s="44"/>
       <c r="F53" s="44"/>
@@ -2702,10 +2675,10 @@
       <c r="A54" s="39"/>
       <c r="B54" s="45"/>
       <c r="C54" s="45" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D54" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E54" s="46"/>
       <c r="F54" s="46"/>
@@ -2716,10 +2689,10 @@
       <c r="A55" s="37"/>
       <c r="B55" s="43"/>
       <c r="C55" s="43" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D55" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E55" s="44"/>
       <c r="F55" s="44"/>
@@ -2730,10 +2703,10 @@
       <c r="A56" s="39"/>
       <c r="B56" s="45"/>
       <c r="C56" s="45" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E56" s="46"/>
       <c r="F56" s="46"/>
@@ -2744,10 +2717,10 @@
       <c r="A57" s="37"/>
       <c r="B57" s="43"/>
       <c r="C57" s="43" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D57" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E57" s="44"/>
       <c r="F57" s="44"/>
@@ -2758,10 +2731,10 @@
       <c r="A58" s="39"/>
       <c r="B58" s="45"/>
       <c r="C58" s="45" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E58" s="46"/>
       <c r="F58" s="46"/>
@@ -2772,10 +2745,10 @@
       <c r="A59" s="37"/>
       <c r="B59" s="43"/>
       <c r="C59" s="43" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E59" s="44"/>
       <c r="F59" s="44"/>
@@ -2786,10 +2759,10 @@
       <c r="A60" s="39"/>
       <c r="B60" s="45"/>
       <c r="C60" s="45" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E60" s="46"/>
       <c r="F60" s="46"/>
@@ -2800,10 +2773,10 @@
       <c r="A61" s="37"/>
       <c r="B61" s="43"/>
       <c r="C61" s="43" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E61" s="44"/>
       <c r="F61" s="44"/>
@@ -2825,7 +2798,7 @@
         <v>6.0</v>
       </c>
       <c r="B63" s="43" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C63" s="43"/>
       <c r="D63" s="44"/>
@@ -2838,13 +2811,13 @@
       <c r="A64" s="39"/>
       <c r="B64" s="45"/>
       <c r="C64" s="45" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E64" s="46" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F64" s="46"/>
       <c r="G64" s="46" t="s">
@@ -2856,10 +2829,10 @@
       <c r="A65" s="37"/>
       <c r="B65" s="43"/>
       <c r="C65" s="43" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E65" s="44"/>
       <c r="F65" s="44"/>
@@ -2870,7 +2843,7 @@
       <c r="A66" s="39"/>
       <c r="B66" s="45"/>
       <c r="C66" s="45" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D66" s="46" t="s">
         <v>10</v>
@@ -2880,20 +2853,20 @@
       </c>
       <c r="F66" s="46"/>
       <c r="G66" s="46" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="H66" s="45" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="37"/>
       <c r="B67" s="43"/>
       <c r="C67" s="43" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D67" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E67" s="44"/>
       <c r="F67" s="44"/>
@@ -2904,10 +2877,10 @@
       <c r="A68" s="39"/>
       <c r="B68" s="45"/>
       <c r="C68" s="45" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D68" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E68" s="46"/>
       <c r="F68" s="46"/>
@@ -2918,10 +2891,10 @@
       <c r="A69" s="37"/>
       <c r="B69" s="43"/>
       <c r="C69" s="43" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E69" s="44"/>
       <c r="F69" s="44"/>
@@ -2932,10 +2905,10 @@
       <c r="A70" s="39"/>
       <c r="B70" s="45"/>
       <c r="C70" s="45" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E70" s="46"/>
       <c r="F70" s="46"/>
@@ -2946,10 +2919,10 @@
       <c r="A71" s="37"/>
       <c r="B71" s="43"/>
       <c r="C71" s="43" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D71" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E71" s="44"/>
       <c r="F71" s="44"/>
@@ -2960,10 +2933,10 @@
       <c r="A72" s="39"/>
       <c r="B72" s="45"/>
       <c r="C72" s="45" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E72" s="46"/>
       <c r="F72" s="46"/>
@@ -2974,10 +2947,10 @@
       <c r="A73" s="37"/>
       <c r="B73" s="43"/>
       <c r="C73" s="43" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D73" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E73" s="44"/>
       <c r="F73" s="44"/>
@@ -3109,26 +3082,26 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G3" s="11"/>
       <c r="I3" s="9" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="J3" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="K3" s="31"/>
+        <v>141</v>
+      </c>
+      <c r="K3" s="32"/>
       <c r="L3" s="18"/>
       <c r="M3" s="18"/>
     </row>
@@ -3137,21 +3110,21 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G4" s="11"/>
       <c r="I4" s="13" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
@@ -3163,31 +3136,31 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="11"/>
       <c r="I5" s="9" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="9" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -3195,21 +3168,21 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G6" s="11"/>
       <c r="I6" s="13" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
@@ -3224,18 +3197,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="G7" s="11"/>
       <c r="I7" s="9" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
@@ -3250,18 +3223,18 @@
         <v>17</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G8" s="11"/>
       <c r="I8" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>10</v>
@@ -3273,7 +3246,7 @@
         <v>20</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
@@ -3281,19 +3254,19 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G9" s="11"/>
       <c r="I9" s="50"/>
@@ -3307,19 +3280,19 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G10" s="11"/>
       <c r="I10" s="45" t="s">
@@ -3335,7 +3308,7 @@
         <v>16</v>
       </c>
       <c r="M10" s="45" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
@@ -3343,35 +3316,35 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G11" s="11"/>
       <c r="I11" s="43" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="43" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="K11" s="43" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="M11" s="43" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
@@ -3379,19 +3352,19 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G12" s="11"/>
       <c r="I12" s="52"/>
@@ -3412,10 +3385,10 @@
       </c>
       <c r="D13" s="56"/>
       <c r="E13" s="44" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G13" s="11"/>
       <c r="I13" s="52"/>
@@ -3436,10 +3409,10 @@
       </c>
       <c r="D14" s="47"/>
       <c r="E14" s="46" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G14" s="11"/>
       <c r="I14" s="52"/>
@@ -3460,10 +3433,10 @@
       </c>
       <c r="D15" s="56"/>
       <c r="E15" s="44" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G15" s="52"/>
       <c r="I15" s="52"/>
@@ -3484,10 +3457,10 @@
       </c>
       <c r="D16" s="47"/>
       <c r="E16" s="46" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G16" s="11"/>
       <c r="I16" s="52"/>
@@ -3501,7 +3474,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C17" s="55"/>
       <c r="D17" s="56"/>
@@ -3866,7 +3839,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="23" t="s">
@@ -3878,13 +3851,13 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="N3" s="18"/>
       <c r="O3" s="9" t="s">
@@ -3897,13 +3870,13 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15" t="s">
@@ -3915,13 +3888,13 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L4" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="N4" s="19"/>
       <c r="O4" s="13" t="s">
@@ -3934,13 +3907,13 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="23" t="s">
@@ -3952,13 +3925,13 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="N5" s="18"/>
       <c r="O5" s="9" t="s">
@@ -3971,13 +3944,13 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15" t="s">
@@ -3989,13 +3962,13 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="N6" s="19"/>
       <c r="O6" s="13" t="s">
@@ -4008,7 +3981,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>14</v>
@@ -4026,13 +3999,13 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="N7" s="18"/>
       <c r="O7" s="9" t="s">
@@ -4045,7 +4018,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>14</v>
@@ -4055,7 +4028,7 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="11"/>
@@ -4063,13 +4036,13 @@
         <v>6.0</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="N8" s="19"/>
       <c r="O8" s="13" t="s">
@@ -4082,13 +4055,13 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23" t="s">
@@ -4100,17 +4073,17 @@
         <v>7.0</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="N9" s="18"/>
       <c r="O9" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P9" s="18"/>
     </row>
@@ -4119,13 +4092,13 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15" t="s">
@@ -4137,17 +4110,17 @@
         <v>8.0</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="N10" s="19"/>
       <c r="O10" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P10" s="19"/>
     </row>
@@ -4156,7 +4129,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -4168,17 +4141,17 @@
         <v>9.0</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="N11" s="18"/>
       <c r="O11" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P11" s="18"/>
     </row>
@@ -4187,16 +4160,16 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>81</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="19"/>
@@ -4205,17 +4178,17 @@
         <v>10.0</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="N12" s="19"/>
       <c r="O12" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P12" s="19"/>
     </row>
@@ -4224,16 +4197,16 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="18"/>
@@ -4242,17 +4215,17 @@
         <v>11.0</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M13" s="25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N13" s="18"/>
       <c r="O13" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P13" s="18"/>
     </row>
@@ -4261,13 +4234,13 @@
         <v>12.0</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
@@ -4277,17 +4250,17 @@
         <v>12.0</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="N14" s="19"/>
       <c r="O14" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P14" s="19"/>
     </row>
@@ -4296,16 +4269,16 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="18"/>
@@ -4314,17 +4287,17 @@
         <v>13.0</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M15" s="25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N15" s="18"/>
       <c r="O15" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P15" s="18"/>
     </row>
@@ -4333,16 +4306,16 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="19"/>
@@ -4351,17 +4324,17 @@
         <v>14.0</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M16" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="N16" s="19"/>
       <c r="O16" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P16" s="19"/>
     </row>
@@ -4370,35 +4343,35 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H17" s="11"/>
       <c r="J17" s="18">
         <v>15.0</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N17" s="18"/>
       <c r="O17" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P17" s="18"/>
     </row>
@@ -4407,16 +4380,16 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="19"/>
@@ -4425,17 +4398,17 @@
         <v>16.0</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="M18" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="N18" s="19"/>
       <c r="O18" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P18" s="19"/>
     </row>
@@ -4444,13 +4417,13 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
@@ -4460,13 +4433,13 @@
         <v>17.0</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>32</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="N19" s="18"/>
       <c r="O19" s="18" t="s">
@@ -4479,13 +4452,13 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
@@ -4495,13 +4468,13 @@
         <v>18.0</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>32</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="N20" s="19"/>
       <c r="O20" s="19" t="s">
@@ -4514,13 +4487,13 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E21" s="23"/>
       <c r="F21" s="23"/>
@@ -4530,13 +4503,13 @@
         <v>19.0</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>36</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="N21" s="18"/>
       <c r="O21" s="18" t="s">
@@ -4549,13 +4522,13 @@
         <v>20.0</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
@@ -4565,13 +4538,13 @@
         <v>20.0</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="N22" s="19"/>
       <c r="O22" s="19" t="s">
@@ -4584,31 +4557,31 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
       <c r="G23" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H23" s="11"/>
       <c r="J23" s="18">
         <v>21.0</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>40</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="N23" s="18"/>
       <c r="O23" s="18" t="s">
@@ -4621,17 +4594,17 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="11"/>
@@ -4639,13 +4612,13 @@
         <v>22.0</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>40</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="N24" s="19"/>
       <c r="O24" s="19" t="s">
@@ -4658,13 +4631,13 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
@@ -4674,13 +4647,13 @@
         <v>23.0</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="N25" s="18"/>
       <c r="O25" s="9" t="s">
@@ -4693,18 +4666,18 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
       <c r="G26" s="13" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H26" s="26"/>
       <c r="I26" s="17"/>
@@ -4712,10 +4685,10 @@
         <v>24.0</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="19"/>
@@ -4727,7 +4700,7 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
@@ -4740,7 +4713,7 @@
         <v>25.0</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>14</v>
@@ -4750,7 +4723,7 @@
       </c>
       <c r="N27" s="18"/>
       <c r="O27" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P27" s="18"/>
     </row>
@@ -4759,22 +4732,22 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="17"/>
@@ -4782,7 +4755,7 @@
         <v>26.0</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="L28" s="13" t="s">
         <v>14</v>
@@ -4792,7 +4765,7 @@
       </c>
       <c r="N28" s="19"/>
       <c r="O28" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P28" s="19"/>
     </row>
@@ -4801,22 +4774,22 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>46</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="17"/>
@@ -4824,7 +4797,7 @@
         <v>27.0</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="L29" s="9" t="s">
         <v>14</v>
@@ -4834,7 +4807,7 @@
       </c>
       <c r="N29" s="18"/>
       <c r="O29" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P29" s="18"/>
     </row>
@@ -4844,19 +4817,19 @@
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>46</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="17"/>
@@ -4864,7 +4837,7 @@
         <v>28.0</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>14</v>
@@ -4874,7 +4847,7 @@
       </c>
       <c r="N30" s="19"/>
       <c r="O30" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P30" s="19"/>
     </row>
@@ -4883,19 +4856,19 @@
         <v>29.0</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G31" s="18"/>
       <c r="H31" s="11"/>
@@ -4904,13 +4877,13 @@
         <v>29.0</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N31" s="23"/>
       <c r="O31" s="18"/>
@@ -4921,17 +4894,17 @@
         <v>30.0</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>88</v>
+        <v>160</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>161</v>
       </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="15" t="s">
-        <v>9</v>
+      <c r="F32" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="G32" s="19"/>
       <c r="H32" s="11"/>
@@ -4940,19 +4913,19 @@
         <v>30.0</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N32" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="O32" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="O32" s="13" t="s">
-        <v>169</v>
       </c>
       <c r="P32" s="19"/>
     </row>
@@ -4961,13 +4934,13 @@
         <v>31.0</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E33" s="23"/>
       <c r="F33" s="10" t="s">
@@ -4980,13 +4953,13 @@
         <v>31.0</v>
       </c>
       <c r="K33" s="18" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N33" s="18"/>
       <c r="O33" s="9" t="s">
@@ -4999,7 +4972,7 @@
         <v>32.0</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
@@ -5012,7 +4985,7 @@
         <v>32.0</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L34" s="28"/>
       <c r="M34" s="19"/>
@@ -5025,18 +4998,18 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E35" s="23"/>
       <c r="F35" s="23"/>
       <c r="G35" s="9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H35" s="11"/>
       <c r="I35" s="17"/>
@@ -5044,13 +5017,13 @@
         <v>33.0</v>
       </c>
       <c r="K35" s="18" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L35" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M35" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N35" s="18"/>
       <c r="O35" s="18">
@@ -5063,13 +5036,13 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="15"/>
@@ -5080,20 +5053,20 @@
         <v>34.0</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L36" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N36" s="19"/>
       <c r="O36" s="19">
         <v>15.0</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
@@ -5101,13 +5074,13 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="23"/>
@@ -5118,20 +5091,20 @@
         <v>35.0</v>
       </c>
       <c r="K37" s="18" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="L37" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M37" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N37" s="18"/>
       <c r="O37" s="18">
         <v>14.0</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
@@ -5139,13 +5112,13 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>
@@ -5156,20 +5129,20 @@
         <v>36.0</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L38" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N38" s="19"/>
       <c r="O38" s="19">
         <v>13.0</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
@@ -5177,13 +5150,13 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="23"/>
@@ -5194,13 +5167,13 @@
         <v>37.0</v>
       </c>
       <c r="K39" s="18" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M39" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N39" s="18"/>
       <c r="O39" s="18">
@@ -5213,13 +5186,13 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="15"/>
@@ -5230,13 +5203,13 @@
         <v>38.0</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L40" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M40" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N40" s="19"/>
       <c r="O40" s="19">
@@ -5249,13 +5222,13 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E41" s="23"/>
       <c r="F41" s="23"/>
@@ -5267,10 +5240,10 @@
       </c>
       <c r="K41" s="18"/>
       <c r="L41" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M41" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N41" s="18"/>
       <c r="O41" s="18">
@@ -5283,13 +5256,13 @@
         <v>40.0</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="15"/>
@@ -5300,13 +5273,13 @@
         <v>40.0</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L42" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M42" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N42" s="19"/>
       <c r="O42" s="19">
@@ -5319,13 +5292,13 @@
         <v>41.0</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E43" s="23"/>
       <c r="F43" s="10" t="s">
@@ -5337,13 +5310,13 @@
         <v>41.0</v>
       </c>
       <c r="K43" s="18" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="L43" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M43" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N43" s="18"/>
       <c r="O43" s="18">
@@ -5356,13 +5329,13 @@
         <v>42.0</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="14" t="s">
@@ -5374,13 +5347,13 @@
         <v>42.0</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="L44" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M44" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N44" s="19"/>
       <c r="O44" s="19">
@@ -5393,13 +5366,13 @@
         <v>43.0</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E45" s="23"/>
       <c r="F45" s="10" t="s">
@@ -5411,13 +5384,13 @@
         <v>43.0</v>
       </c>
       <c r="K45" s="18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L45" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M45" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N45" s="18"/>
       <c r="O45" s="18">
@@ -5430,13 +5403,13 @@
         <v>44.0</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="14" t="s">
@@ -5448,20 +5421,20 @@
         <v>44.0</v>
       </c>
       <c r="K46" s="19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="L46" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M46" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N46" s="19"/>
       <c r="O46" s="19">
         <v>5.0</v>
       </c>
       <c r="P46" s="19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
@@ -5469,7 +5442,7 @@
         <v>45.0</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="10"/>
@@ -5482,10 +5455,10 @@
       </c>
       <c r="K47" s="18"/>
       <c r="L47" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M47" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N47" s="18"/>
       <c r="O47" s="18">
@@ -5498,7 +5471,7 @@
         <v>46.0</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C48" s="15"/>
       <c r="D48" s="14"/>
@@ -5510,13 +5483,13 @@
         <v>46.0</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M48" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N48" s="19"/>
       <c r="O48" s="19">
@@ -5529,7 +5502,7 @@
         <v>47.0</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -5541,13 +5514,13 @@
         <v>47.0</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M49" s="18" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N49" s="18"/>
       <c r="O49" s="18">
@@ -5560,7 +5533,7 @@
         <v>48.0</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
@@ -5572,13 +5545,13 @@
         <v>48.0</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L50" s="19" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M50" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N50" s="19"/>
       <c r="O50" s="19">
@@ -5591,7 +5564,7 @@
         <v>49.0</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C51" s="23"/>
       <c r="D51" s="23"/>
@@ -5603,13 +5576,13 @@
         <v>49.0</v>
       </c>
       <c r="K51" s="18" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M51" s="25" t="s">
-        <v>80</v>
+        <v>144</v>
+      </c>
+      <c r="M51" s="31" t="s">
+        <v>77</v>
       </c>
       <c r="N51" s="9">
         <v>9.0</v>
@@ -5624,13 +5597,13 @@
         <v>50.0</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
@@ -5640,10 +5613,10 @@
         <v>50.0</v>
       </c>
       <c r="K52" s="19" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M52" s="19"/>
       <c r="N52" s="19"/>
@@ -5655,13 +5628,13 @@
         <v>51.0</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E53" s="23"/>
       <c r="F53" s="23"/>
@@ -5671,13 +5644,13 @@
         <v>51.0</v>
       </c>
       <c r="K53" s="18" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L53" s="18" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M53" s="23" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N53" s="18"/>
       <c r="O53" s="18" t="s">
@@ -5690,7 +5663,7 @@
         <v>52.0</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C54" s="15"/>
       <c r="D54" s="15"/>
@@ -5702,13 +5675,13 @@
         <v>52.0</v>
       </c>
       <c r="K54" s="19" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N54" s="19"/>
       <c r="O54" s="13" t="s">
@@ -5721,19 +5694,19 @@
         <v>53.0</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G55" s="18"/>
       <c r="H55" s="11"/>
@@ -5741,10 +5714,10 @@
         <v>53.0</v>
       </c>
       <c r="K55" s="18" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M55" s="18"/>
       <c r="N55" s="18"/>
@@ -5756,7 +5729,7 @@
         <v>54.0</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
@@ -5768,13 +5741,13 @@
         <v>54.0</v>
       </c>
       <c r="K56" s="19" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="N56" s="19"/>
       <c r="O56" s="13" t="s">
@@ -5787,7 +5760,7 @@
         <v>55.0</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>25</v>
@@ -5796,7 +5769,7 @@
         <v>26</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>28</v>
@@ -5818,7 +5791,7 @@
         <v>56.0</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15"/>
@@ -5830,7 +5803,7 @@
         <v>56.0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L58" s="13" t="s">
         <v>25</v>
@@ -5839,7 +5812,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="13" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O58" s="13" t="s">
         <v>31</v>
@@ -5851,17 +5824,17 @@
         <v>57.0</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="10" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G59" s="18"/>
       <c r="H59" s="11"/>
@@ -5869,13 +5842,13 @@
         <v>57.0</v>
       </c>
       <c r="K59" s="18" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="M59" s="31" t="s">
-        <v>226</v>
+        <v>218</v>
+      </c>
+      <c r="M59" s="32" t="s">
+        <v>219</v>
       </c>
       <c r="N59" s="18"/>
       <c r="O59" s="18"/>
@@ -5886,17 +5859,17 @@
         <v>58.0</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G60" s="19"/>
       <c r="H60" s="11"/>
@@ -5904,13 +5877,13 @@
         <v>58.0</v>
       </c>
       <c r="K60" s="19" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M60" s="13" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="N60" s="19"/>
       <c r="O60" s="19"/>
@@ -5921,17 +5894,17 @@
         <v>59.0</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G61" s="18"/>
       <c r="H61" s="11"/>
@@ -5939,13 +5912,13 @@
         <v>59.0</v>
       </c>
       <c r="K61" s="18" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="M61" s="31" t="s">
-        <v>226</v>
+        <v>218</v>
+      </c>
+      <c r="M61" s="32" t="s">
+        <v>219</v>
       </c>
       <c r="N61" s="18"/>
       <c r="O61" s="18"/>
@@ -5956,17 +5929,17 @@
         <v>60.0</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G62" s="19"/>
       <c r="H62" s="11"/>
@@ -5974,13 +5947,13 @@
         <v>60.0</v>
       </c>
       <c r="K62" s="19" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="M62" s="13" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="N62" s="19"/>
       <c r="O62" s="19"/>
@@ -5991,7 +5964,7 @@
         <v>61.0</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C63" s="23"/>
       <c r="D63" s="23"/>
@@ -6003,13 +5976,13 @@
         <v>61.0</v>
       </c>
       <c r="K63" s="18" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="M63" s="31" t="s">
-        <v>233</v>
+        <v>154</v>
+      </c>
+      <c r="M63" s="32" t="s">
+        <v>226</v>
       </c>
       <c r="N63" s="18"/>
       <c r="O63" s="9" t="s">
@@ -6022,19 +5995,19 @@
         <v>62.0</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G64" s="13"/>
       <c r="H64" s="11"/>
@@ -6042,13 +6015,13 @@
         <v>62.0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="13" t="s">
@@ -6061,27 +6034,27 @@
         <v>63.0</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D65" s="32" t="s">
-        <v>143</v>
+        <v>84</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="10" t="s">
         <v>46</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="H65" s="11"/>
       <c r="J65" s="18">
         <v>63.0</v>
       </c>
       <c r="K65" s="18" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="L65" s="18"/>
       <c r="M65" s="18"/>
@@ -6094,17 +6067,17 @@
         <v>64.0</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C66" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D66" s="14" t="s">
         <v>50</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>51</v>
       </c>
       <c r="E66" s="15"/>
       <c r="F66" s="14" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G66" s="19"/>
       <c r="H66" s="11"/>
@@ -6112,7 +6085,7 @@
         <v>64.0</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="L66" s="19"/>
       <c r="M66" s="19"/>
@@ -6237,10 +6210,10 @@
         <v>11</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F3" s="11"/>
       <c r="H3" s="18">
@@ -6257,10 +6230,10 @@
         <v>2.0</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>50</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>51</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>13</v>
@@ -6280,14 +6253,14 @@
       <c r="A5" s="18">
         <v>3.0</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>245</v>
+      <c r="D5" s="25" t="s">
+        <v>238</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="11"/>
@@ -6305,13 +6278,13 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="D6" s="14" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E6" s="19"/>
       <c r="F6" s="11"/>
@@ -6328,14 +6301,14 @@
       <c r="A7" s="18">
         <v>5.0</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>247</v>
+      <c r="D7" s="25" t="s">
+        <v>240</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="11"/>
@@ -6353,13 +6326,13 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="D8" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E8" s="19"/>
       <c r="F8" s="11"/>
@@ -6376,14 +6349,14 @@
       <c r="A9" s="18">
         <v>7.0</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>249</v>
+      <c r="D9" s="25" t="s">
+        <v>242</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="11"/>
@@ -6401,13 +6374,13 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E10" s="19"/>
       <c r="F10" s="11"/>
@@ -6424,14 +6397,14 @@
       <c r="A11" s="18">
         <v>9.0</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>251</v>
+      <c r="D11" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="11"/>
@@ -6449,13 +6422,13 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="D12" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="11"/>
@@ -6472,14 +6445,14 @@
       <c r="A13" s="18">
         <v>11.0</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13" s="11"/>
@@ -6503,7 +6476,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E14" s="19"/>
       <c r="F14" s="11"/>
@@ -6520,14 +6493,14 @@
       <c r="A15" s="18">
         <v>13.0</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="11"/>
@@ -6535,16 +6508,16 @@
         <v>13.0</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K15" s="9">
         <v>4.0</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M15" s="9"/>
     </row>
@@ -6559,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="11"/>
@@ -6567,16 +6540,16 @@
         <v>14.0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K16" s="13">
         <v>5.0</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M16" s="13"/>
     </row>
@@ -6584,14 +6557,14 @@
       <c r="A17" s="18">
         <v>15.0</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="11"/>
@@ -6599,16 +6572,16 @@
         <v>15.0</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K17" s="9">
         <v>6.0</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M17" s="9"/>
     </row>
@@ -6623,7 +6596,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="11"/>
@@ -6631,16 +6604,16 @@
         <v>16.0</v>
       </c>
       <c r="I18" s="35" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J18" s="36" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K18" s="35">
         <v>7.0</v>
       </c>
       <c r="L18" s="35" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M18" s="35"/>
     </row>
@@ -6656,7 +6629,7 @@
     <row r="20" ht="12.75" customHeight="1">
       <c r="F20" s="17"/>
       <c r="H20" s="39" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I20" s="39" t="s">
         <v>10</v>
@@ -6666,10 +6639,10 @@
       </c>
       <c r="K20" s="40"/>
       <c r="L20" s="39" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
@@ -6785,7 +6758,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F3" s="11"/>
       <c r="H3" s="18">
@@ -6793,7 +6766,7 @@
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K3" s="18"/>
       <c r="L3" s="18"/>
@@ -6812,17 +6785,17 @@
         <v>13</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" s="11"/>
       <c r="H4" s="19">
         <v>2.0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>19</v>
@@ -6840,20 +6813,20 @@
         <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5" s="11"/>
       <c r="H5" s="18">
         <v>3.0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>23</v>
@@ -6871,20 +6844,20 @@
         <v>11</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F6" s="11"/>
       <c r="H6" s="19">
         <v>4.0</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>24</v>
@@ -6902,20 +6875,20 @@
         <v>11</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F7" s="11"/>
       <c r="H7" s="18">
         <v>5.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>16</v>
@@ -6933,20 +6906,20 @@
         <v>11</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F8" s="11"/>
       <c r="H8" s="19">
         <v>6.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K8" s="13" t="s">
         <v>20</v>
@@ -6964,23 +6937,23 @@
         <v>11</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="11"/>
       <c r="H9" s="18">
         <v>7.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L9" s="18"/>
     </row>
@@ -6995,23 +6968,23 @@
         <v>11</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F10" s="11"/>
       <c r="H10" s="19">
         <v>8.0</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L10" s="19"/>
     </row>
@@ -7026,23 +6999,23 @@
         <v>11</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F11" s="11"/>
       <c r="H11" s="18">
         <v>9.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L11" s="18"/>
     </row>
@@ -7057,23 +7030,23 @@
         <v>11</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F12" s="11"/>
       <c r="H12" s="19">
         <v>10.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L12" s="19"/>
     </row>
@@ -7081,10 +7054,10 @@
       <c r="A13" s="18">
         <v>11.0</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="32"/>
+      <c r="B13" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="25"/>
       <c r="D13" s="23"/>
       <c r="E13" s="18"/>
       <c r="F13" s="11"/>
@@ -7098,10 +7071,10 @@
         <v>11</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
@@ -7110,7 +7083,7 @@
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="27" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="19"/>
@@ -7120,7 +7093,7 @@
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="41" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -7173,7 +7146,7 @@
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -7194,13 +7167,13 @@
         <v>16.0</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="11"/>
@@ -7216,10 +7189,10 @@
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F4" s="11"/>
     </row>
@@ -7234,10 +7207,10 @@
         <v>11</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F5" s="11"/>
     </row>
@@ -7252,10 +7225,10 @@
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F6" s="11"/>
     </row>
@@ -7270,10 +7243,10 @@
         <v>11</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F7" s="11"/>
     </row>
@@ -7288,10 +7261,10 @@
         <v>11</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F8" s="11"/>
     </row>
@@ -7306,10 +7279,10 @@
         <v>11</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F9" s="11"/>
     </row>
@@ -7324,10 +7297,10 @@
         <v>11</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F10" s="11"/>
     </row>
@@ -7336,7 +7309,7 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -7348,7 +7321,7 @@
         <v>7.0</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -7360,7 +7333,7 @@
         <v>6.0</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -7372,7 +7345,7 @@
         <v>5.0</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
@@ -7384,7 +7357,7 @@
         <v>4.0</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -7396,7 +7369,7 @@
         <v>3.0</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -7408,7 +7381,7 @@
         <v>2.0</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -7420,7 +7393,7 @@
         <v>1.0</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -7474,7 +7447,7 @@
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -7495,16 +7468,16 @@
         <v>16.0</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F3" s="11"/>
     </row>
@@ -7519,10 +7492,10 @@
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F4" s="11"/>
     </row>
@@ -7537,10 +7510,10 @@
         <v>11</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F5" s="11"/>
     </row>
@@ -7555,10 +7528,10 @@
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F6" s="11"/>
     </row>
@@ -7573,10 +7546,10 @@
         <v>11</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F7" s="11"/>
     </row>
@@ -7591,10 +7564,10 @@
         <v>11</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F8" s="11"/>
     </row>
@@ -7609,7 +7582,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="11"/>
@@ -7625,10 +7598,10 @@
         <v>11</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F10" s="11"/>
     </row>
@@ -7637,16 +7610,16 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F11" s="11"/>
     </row>
@@ -7655,16 +7628,16 @@
         <v>7.0</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F12" s="11"/>
     </row>
@@ -7673,16 +7646,16 @@
         <v>6.0</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F13" s="11"/>
     </row>
@@ -7691,16 +7664,16 @@
         <v>5.0</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F14" s="11"/>
     </row>
@@ -7709,13 +7682,13 @@
         <v>4.0</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="11"/>
@@ -7725,16 +7698,16 @@
         <v>3.0</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F16" s="11"/>
     </row>
@@ -7743,16 +7716,16 @@
         <v>2.0</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F17" s="11"/>
     </row>
@@ -7761,16 +7734,16 @@
         <v>1.0</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F18" s="11"/>
     </row>
@@ -7859,70 +7832,70 @@
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C3" s="9">
         <v>1.0</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="J3" s="11"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C4" s="13">
         <v>2.0</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="J4" s="11"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C5" s="9">
         <v>3.0</v>
@@ -7989,7 +7962,7 @@
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>4</v>
@@ -8019,10 +7992,10 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>10</v>
@@ -8032,10 +8005,10 @@
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I3" s="11"/>
     </row>
@@ -8043,10 +8016,10 @@
       <c r="A4" s="12"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="14"/>
@@ -8058,20 +8031,20 @@
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I5" s="11"/>
     </row>
@@ -8091,10 +8064,10 @@
         <v>2.0</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>10</v>
@@ -8104,10 +8077,10 @@
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I7" s="11"/>
     </row>
@@ -8115,10 +8088,10 @@
       <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="14"/>
@@ -8130,20 +8103,20 @@
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="I9" s="11"/>
     </row>
@@ -8163,10 +8136,10 @@
         <v>3.0</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>10</v>
@@ -8176,7 +8149,7 @@
       </c>
       <c r="F11" s="44"/>
       <c r="G11" s="44" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="H11" s="43"/>
       <c r="I11" s="17"/>
@@ -8185,10 +8158,10 @@
       <c r="A12" s="39"/>
       <c r="B12" s="45"/>
       <c r="C12" s="45" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E12" s="47"/>
       <c r="F12" s="46"/>
@@ -8200,10 +8173,10 @@
       <c r="A13" s="37"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E13" s="44"/>
       <c r="F13" s="44"/>
@@ -8227,23 +8200,23 @@
         <v>4.0</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="44" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I15" s="17"/>
     </row>
@@ -8251,7 +8224,7 @@
       <c r="A16" s="39"/>
       <c r="B16" s="45"/>
       <c r="C16" s="45" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D16" s="46" t="s">
         <v>14</v>
@@ -8261,7 +8234,7 @@
       </c>
       <c r="F16" s="46"/>
       <c r="G16" s="46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H16" s="45"/>
       <c r="I16" s="17"/>
@@ -8270,17 +8243,17 @@
       <c r="A17" s="37"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="44" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="17"/>
@@ -8289,17 +8262,17 @@
       <c r="A18" s="39"/>
       <c r="B18" s="45"/>
       <c r="C18" s="45" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F18" s="46"/>
       <c r="G18" s="46" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H18" s="45"/>
       <c r="I18" s="17"/>
@@ -8320,23 +8293,23 @@
         <v>5.0</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="F20" s="46"/>
       <c r="G20" s="46" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="H20" s="45" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I20" s="17"/>
     </row>
@@ -8344,7 +8317,7 @@
       <c r="A21" s="37"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D21" s="44" t="s">
         <v>14</v>
@@ -8354,7 +8327,7 @@
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H21" s="43"/>
       <c r="I21" s="17"/>
@@ -8363,17 +8336,17 @@
       <c r="A22" s="39"/>
       <c r="B22" s="45"/>
       <c r="C22" s="45" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F22" s="46"/>
       <c r="G22" s="46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H22" s="45"/>
       <c r="I22" s="17"/>
@@ -8382,10 +8355,10 @@
       <c r="A23" s="37"/>
       <c r="B23" s="43"/>
       <c r="C23" s="43" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E23" s="44"/>
       <c r="F23" s="44"/>
@@ -8409,23 +8382,23 @@
         <v>6.0</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="F25" s="44"/>
       <c r="G25" s="44" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="H25" s="43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I25" s="17"/>
     </row>
@@ -8433,7 +8406,7 @@
       <c r="A26" s="39"/>
       <c r="B26" s="45"/>
       <c r="C26" s="45" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D26" s="46" t="s">
         <v>14</v>
@@ -8443,7 +8416,7 @@
       </c>
       <c r="F26" s="46"/>
       <c r="G26" s="46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H26" s="45"/>
       <c r="I26" s="17"/>
@@ -8452,17 +8425,17 @@
       <c r="A27" s="37"/>
       <c r="B27" s="43"/>
       <c r="C27" s="43" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F27" s="44"/>
       <c r="G27" s="44" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H27" s="43"/>
       <c r="I27" s="17"/>
@@ -8471,10 +8444,10 @@
       <c r="A28" s="39"/>
       <c r="B28" s="45"/>
       <c r="C28" s="45" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E28" s="46"/>
       <c r="F28" s="46"/>
@@ -8498,23 +8471,23 @@
         <v>7.0</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>262</v>
+        <v>85</v>
       </c>
       <c r="F30" s="46"/>
       <c r="G30" s="46" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H30" s="45" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I30" s="17"/>
     </row>
@@ -8522,7 +8495,7 @@
       <c r="A31" s="37"/>
       <c r="B31" s="43"/>
       <c r="C31" s="43" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D31" s="44" t="s">
         <v>14</v>
@@ -8532,7 +8505,7 @@
       </c>
       <c r="F31" s="44"/>
       <c r="G31" s="44" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H31" s="43"/>
       <c r="I31" s="17"/>
@@ -8541,17 +8514,17 @@
       <c r="A32" s="39"/>
       <c r="B32" s="45"/>
       <c r="C32" s="45" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F32" s="46"/>
       <c r="G32" s="46" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H32" s="45"/>
       <c r="I32" s="17"/>
@@ -8560,10 +8533,10 @@
       <c r="A33" s="37"/>
       <c r="B33" s="43"/>
       <c r="C33" s="43" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E33" s="44"/>
       <c r="F33" s="44"/>
@@ -8587,13 +8560,13 @@
         <v>8.0</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E35" s="44"/>
       <c r="F35" s="44"/>
@@ -8605,10 +8578,10 @@
       <c r="A36" s="39"/>
       <c r="B36" s="45"/>
       <c r="C36" s="45" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E36" s="46"/>
       <c r="F36" s="46"/>
@@ -8620,10 +8593,10 @@
       <c r="A37" s="37"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E37" s="44"/>
       <c r="F37" s="44"/>
@@ -8635,10 +8608,10 @@
       <c r="A38" s="39"/>
       <c r="B38" s="45"/>
       <c r="C38" s="45" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E38" s="46"/>
       <c r="F38" s="46"/>
@@ -8662,13 +8635,13 @@
         <v>9.0</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E40" s="46"/>
       <c r="F40" s="46"/>
@@ -8680,7 +8653,7 @@
       <c r="A41" s="37"/>
       <c r="B41" s="43"/>
       <c r="C41" s="43" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D41" s="44" t="s">
         <v>10</v>
@@ -8690,10 +8663,10 @@
       </c>
       <c r="F41" s="44"/>
       <c r="G41" s="44" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="H41" s="43" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I41" s="17"/>
     </row>
@@ -8701,10 +8674,10 @@
       <c r="A42" s="39"/>
       <c r="B42" s="45"/>
       <c r="C42" s="45" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D42" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E42" s="46"/>
       <c r="F42" s="46"/>
@@ -8716,16 +8689,16 @@
       <c r="A43" s="37"/>
       <c r="B43" s="43"/>
       <c r="C43" s="43" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D43" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E43" s="44"/>
       <c r="F43" s="44"/>
       <c r="G43" s="44"/>
       <c r="H43" s="49" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="I43" s="17"/>
     </row>
@@ -8733,10 +8706,10 @@
       <c r="A44" s="39"/>
       <c r="B44" s="45"/>
       <c r="C44" s="45" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E44" s="46"/>
       <c r="F44" s="46"/>
@@ -8748,16 +8721,16 @@
       <c r="A45" s="37"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
       <c r="G45" s="44"/>
       <c r="H45" s="49" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="I45" s="17"/>
     </row>
@@ -8765,10 +8738,10 @@
       <c r="A46" s="39"/>
       <c r="B46" s="45"/>
       <c r="C46" s="45" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E46" s="46"/>
       <c r="F46" s="46"/>
@@ -8780,10 +8753,10 @@
       <c r="A47" s="37"/>
       <c r="B47" s="43"/>
       <c r="C47" s="43" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -8795,10 +8768,10 @@
       <c r="A48" s="39"/>
       <c r="B48" s="45"/>
       <c r="C48" s="45" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E48" s="46"/>
       <c r="F48" s="46"/>
@@ -8810,10 +8783,10 @@
       <c r="A49" s="37"/>
       <c r="B49" s="43"/>
       <c r="C49" s="43" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E49" s="44"/>
       <c r="F49" s="44"/>
